--- a/data/output/evaluasi_75.xlsx
+++ b/data/output/evaluasi_75.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="7500" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="7501" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="7504" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="7502" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="7504" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="7571" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="7501" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="7505" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="7503" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7571" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +481,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-6.120052022151032</v>
+        <v>-6.736694090107413</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -488,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -507,7 +509,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-6.702251542673646</v>
+        <v>-11.04601296224089</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -516,7 +518,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -531,20 +533,300 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.964541700947795</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.756418223244827</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q1-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>-10.47783674189591</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D6" t="n">
+        <v>-7.998298741763602</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.816240022033612</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>75</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.39641323339417</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q2-25 vs q-to-q_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>75</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-26.78348305189774</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>75</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.618186992254111</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-8.839507650659165</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>75</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.679868762168523</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>75</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.121904103975096</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>75</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gorontalo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7.358547475900787</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
         </is>
       </c>
     </row>
@@ -559,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,11 +878,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7501</v>
+        <v>7504</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Boalemo</t>
+          <t>Kabupaten Bone Bolango</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -609,44 +891,156 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11686.65400302398</v>
+        <v>-2.095437997649704</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7501</v>
+        <v>7504</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Boalemo</t>
+          <t>Kabupaten Bone Bolango</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1435586256896698</v>
+        <v>-2.120935182478926</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14.0014502654777</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-9.59576484274551</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-8.363680853308129</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.593827761535274</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -661,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,20 +1101,76 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02427987148905125</v>
+        <v>-0.7980753645069064</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.068572941406259</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-7.635659786734419</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -735,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,57 +1222,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7504</v>
+        <v>7501</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bone Bolango</t>
+          <t>Kabupaten Boalemo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.140099523958587</v>
+        <v>-14.55219857502112</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7504</v>
+        <v>7501</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bone Bolango</t>
+          <t>Kabupaten Boalemo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6782012844655916</v>
+        <v>-6.805811196777833</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7501</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Boalemo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3424830540186404</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7501</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Boalemo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.03643370114606106</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7501</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Boalemo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.323558031944785</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -837,6 +1371,434 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8.711216125046981</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.790442764542194</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.312744255875792</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.534165684476838</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.977482645738244</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.811227266387349</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>46.12954155678707</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.59797523869771</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.895163591361975</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>31.52666301533624</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.879725263442251</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.0823235000852</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -883,20 +1845,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.5373112308474436</v>
+        <v>8.348957906432078</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -911,20 +1873,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.075492470763177</v>
+        <v>8.203381895919556</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_75.xlsx
+++ b/data/output/evaluasi_75.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
